--- a/calendario_sala.xlsx
+++ b/calendario_sala.xlsx
@@ -466,11 +466,6 @@
           <t>08:30 - 10:00</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>eldercio</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -478,11 +473,6 @@
           <t>10:15 - 11:45</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>matias</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -490,9 +480,9 @@
           <t>12:00 - 14:15</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>elder</t>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>vicente gay</t>
         </is>
       </c>
     </row>

--- a/calendario_sala.xlsx
+++ b/calendario_sala.xlsx
@@ -480,9 +480,9 @@
           <t>12:00 - 14:15</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>vicente gay</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>elder</t>
         </is>
       </c>
     </row>

--- a/calendario_sala.xlsx
+++ b/calendario_sala.xlsx
@@ -480,11 +480,6 @@
           <t>12:00 - 14:15</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>elder</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/calendario_sala.xlsx
+++ b/calendario_sala.xlsx
@@ -466,6 +466,16 @@
           <t>08:30 - 10:00</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>vicente</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>vicentepistola</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
